--- a/docs/xlsx/Sport_Mate.xlsx
+++ b/docs/xlsx/Sport_Mate.xlsx
@@ -8,15 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
-    <sheet name="Features" sheetId="2" r:id="rId2"/>
-    <sheet name="Roles" sheetId="3" r:id="rId3"/>
-    <sheet name="Authorization" sheetId="4" r:id="rId4"/>
-    <sheet name="Screen Visibility" sheetId="5" r:id="rId5"/>
-    <sheet name="Business Rules" sheetId="6" r:id="rId6"/>
+    <sheet name="Delivery Plan" sheetId="2" r:id="rId2"/>
+    <sheet name="Features" sheetId="3" r:id="rId3"/>
+    <sheet name="Roles" sheetId="4" r:id="rId4"/>
+    <sheet name="Authorization" sheetId="5" r:id="rId5"/>
+    <sheet name="Screen Visibility" sheetId="6" r:id="rId6"/>
+    <sheet name="Business Rules" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Features!$A$1:$L$79</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">Features!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Features!$A$1:$O$79</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">Features!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
     <author>Sport Mate</author>
   </authors>
   <commentList>
-    <comment ref="L1" authorId="0">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -49,7 +50,19 @@
             <rFont val="SimSun"/>
             <charset val="134"/>
           </rPr>
-          <t>Fill in the team member responsible for this feature.</t>
+          <t>Done / Processing / Not Start. Update as work progresses.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="SimSun"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Team member who owns this feature (list from the Delivery Plan sheet).</t>
         </r>
       </text>
     </comment>
@@ -58,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="818">
   <si>
     <t>Sport Mate — Feature &amp; Role Specification</t>
   </si>
@@ -72,13 +85,13 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0</t>
+    <t>1.1</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-11</t>
+    <t>2026-10-14</t>
   </si>
   <si>
     <t>Scope</t>
@@ -87,6 +100,18 @@
     <t>78 features (F01–F78), mapped one-to-one to use cases UC-001–UC-078</t>
   </si>
   <si>
+    <t>Schedule</t>
+  </si>
+  <si>
+    <t>Start 07/09/2026 · Interaction 1 due 13/10/2026 · Interaction 2 due 21/10/2026 · Interaction 3 due 27/10/2026</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Minh · Lê Huỳnh Nhựt Khanh · Huỳnh Trần Phước Sang · Trần Thị Hồng Mai · Trương Đoàn Minh Phúc</t>
+  </si>
+  <si>
     <t>Tech stack</t>
   </si>
   <si>
@@ -102,10 +127,10 @@
     <t>How to use this workbook</t>
   </si>
   <si>
-    <t>• Features sheet: one row per feature (F01–F78). Fill in the yellow Assignee column (L).</t>
-  </si>
-  <si>
-    <t>• The progress table below updates automatically from the Assignee column.</t>
+    <t>• Features sheet: one row per feature (F01–F78) with Interaction (L), Deadline (M), Status (N) and Assignee (O).</t>
+  </si>
+  <si>
+    <t>• Update Status as work progresses; the progress tables here and on the Delivery Plan sheet recalculate automatically.</t>
   </si>
   <si>
     <t>• API paths are relative to /api/v1. "(proposed)" marks endpoints not defined in API_DESIGN.md.</t>
@@ -132,10 +157,10 @@
     <t>Features</t>
   </si>
   <si>
-    <t>Assigned</t>
-  </si>
-  <si>
-    <t>% assigned</t>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>% done</t>
   </si>
   <si>
     <t>Roles involved</t>
@@ -229,6 +254,105 @@
   </si>
   <si>
     <t>F01–F78</t>
+  </si>
+  <si>
+    <t>Delivery Plan</t>
+  </si>
+  <si>
+    <t>Project start</t>
+  </si>
+  <si>
+    <t>Interaction schedule</t>
+  </si>
+  <si>
+    <t>Interaction</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>Deadline</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Processing</t>
+  </si>
+  <si>
+    <t>Not Start</t>
+  </si>
+  <si>
+    <t>Interaction 1</t>
+  </si>
+  <si>
+    <t>F01–F09, F18–F30, F38–F42, F46–F52, F73–F75</t>
+  </si>
+  <si>
+    <t>Interaction 2</t>
+  </si>
+  <si>
+    <t>F10–F12, F31–F33, F43–F45, F53–F67</t>
+  </si>
+  <si>
+    <t>Interaction 3</t>
+  </si>
+  <si>
+    <t>F13–F17, F34–F37, F68–F72, F76–F78</t>
+  </si>
+  <si>
+    <t>Team assignment</t>
+  </si>
+  <si>
+    <t>Member</t>
+  </si>
+  <si>
+    <t>GitHub</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Minh</t>
+  </si>
+  <si>
+    <t>Minh2005</t>
+  </si>
+  <si>
+    <t>F01–F17</t>
+  </si>
+  <si>
+    <t>Lê Huỳnh Nhựt Khanh</t>
+  </si>
+  <si>
+    <t>lehuynhnhutkhanh2004</t>
+  </si>
+  <si>
+    <t>F26–F37, F65–F67</t>
+  </si>
+  <si>
+    <t>Huỳnh Trần Phước Sang</t>
+  </si>
+  <si>
+    <t>sengggggg</t>
+  </si>
+  <si>
+    <t>F18–F25, F46–F50, F56–F60, F76–F78</t>
+  </si>
+  <si>
+    <t>Trần Thị Hồng Mai</t>
+  </si>
+  <si>
+    <t>HM126-m</t>
+  </si>
+  <si>
+    <t>F61–F64, F68–F75</t>
+  </si>
+  <si>
+    <t>Trương Đoàn Minh Phúc</t>
+  </si>
+  <si>
+    <t>nilernous</t>
+  </si>
+  <si>
+    <t>F38–F45, F51–F55</t>
   </si>
   <si>
     <t>No.</t>
@@ -2413,11 +2537,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -3120,7 +3245,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3153,20 +3278,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="178" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3219,7 +3354,7 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3239,8 +3374,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-          <bgColor rgb="FFFCE4D6"/>
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3249,6 +3384,14 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFEDEDED"/>
           <bgColor rgb="FFEDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
+          <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3574,7 +3717,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -3585,277 +3728,247 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" spans="1:2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="22" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="22" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" ht="15.6" spans="1:2">
-      <c r="A10" s="16" t="s">
+    <row r="9" spans="1:2">
+      <c r="A9" s="15" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="15" t="s">
+      <c r="B9" s="22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="15" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="15" t="s">
         <v>15</v>
       </c>
+      <c r="B10" s="22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" ht="15.6" spans="1:2">
+      <c r="A12" s="17" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="15" t="s">
-        <v>16</v>
+      <c r="A13" s="22" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="15" t="s">
-        <v>17</v>
+      <c r="A14" s="22" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" ht="15.6" spans="1:6">
+      <c r="A20" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="9">
+        <f>COUNTIF(Features!$B$2:$B$79,A22)</f>
+        <v>5</v>
+      </c>
+      <c r="D22" s="9">
+        <f>COUNTIFS(Features!$B$2:$B$79,A22,Features!$N$2:$N$79,"Done")</f>
+        <v>5</v>
+      </c>
+      <c r="E22" s="20">
+        <f t="shared" ref="E22:E33" si="0">IF(C22=0,0,D22/C22)</f>
+        <v>1</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="9">
+        <f>COUNTIF(Features!$B$2:$B$79,A23)</f>
+        <v>12</v>
+      </c>
+      <c r="D23" s="9">
+        <f>COUNTIFS(Features!$B$2:$B$79,A23,Features!$N$2:$N$79,"Done")</f>
+        <v>4</v>
+      </c>
+      <c r="E23" s="20">
+        <f t="shared" si="0"/>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="9">
+        <f>COUNTIF(Features!$B$2:$B$79,A24)</f>
+        <v>25</v>
+      </c>
+      <c r="D24" s="9">
+        <f>COUNTIFS(Features!$B$2:$B$79,A24,Features!$N$2:$N$79,"Done")</f>
         <v>18</v>
       </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" ht="15.6" spans="1:6">
-      <c r="A18" s="16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="9">
-        <f>COUNTIF(Features!$B$2:$B$79,A20)</f>
-        <v>5</v>
-      </c>
-      <c r="D20" s="9">
-        <f>COUNTIFS(Features!$B$2:$B$79,A20,Features!$L$2:$L$79,"&lt;&gt;")</f>
+      <c r="E24" s="20">
+        <f t="shared" si="0"/>
+        <v>0.72</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="9">
+        <f>COUNTIF(Features!$B$2:$B$79,A25)</f>
+        <v>3</v>
+      </c>
+      <c r="D25" s="9">
+        <f>COUNTIFS(Features!$B$2:$B$79,A25,Features!$N$2:$N$79,"Done")</f>
         <v>0</v>
       </c>
-      <c r="E20" s="18">
-        <f t="shared" ref="E20:E31" si="0">IF(C20=0,0,D20/C20)</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="9">
-        <f>COUNTIF(Features!$B$2:$B$79,A21)</f>
-        <v>12</v>
-      </c>
-      <c r="D21" s="9">
-        <f>COUNTIFS(Features!$B$2:$B$79,A21,Features!$L$2:$L$79,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="18">
+      <c r="E25" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="9">
-        <f>COUNTIF(Features!$B$2:$B$79,A22)</f>
-        <v>25</v>
-      </c>
-      <c r="D22" s="9">
-        <f>COUNTIFS(Features!$B$2:$B$79,A22,Features!$L$2:$L$79,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" s="9">
-        <f>COUNTIF(Features!$B$2:$B$79,A23)</f>
-        <v>3</v>
-      </c>
-      <c r="D23" s="9">
-        <f>COUNTIFS(Features!$B$2:$B$79,A23,Features!$L$2:$L$79,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="9">
-        <f>COUNTIF(Features!$B$2:$B$79,A24)</f>
-        <v>5</v>
-      </c>
-      <c r="D24" s="9">
-        <f>COUNTIFS(Features!$B$2:$B$79,A24,Features!$L$2:$L$79,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="9">
-        <f>COUNTIF(Features!$B$2:$B$79,A25)</f>
-        <v>7</v>
-      </c>
-      <c r="D25" s="9">
-        <f>COUNTIFS(Features!$B$2:$B$79,A25,Features!$L$2:$L$79,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="C26" s="9">
         <f>COUNTIF(Features!$B$2:$B$79,A26)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D26" s="9">
-        <f>COUNTIFS(Features!$B$2:$B$79,A26,Features!$L$2:$L$79,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="18">
+        <f>COUNTIFS(Features!$B$2:$B$79,A26,Features!$N$2:$N$79,"Done")</f>
+        <v>5</v>
+      </c>
+      <c r="E26" s="20">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -3870,61 +3983,61 @@
         <v>7</v>
       </c>
       <c r="D27" s="9">
-        <f>COUNTIFS(Features!$B$2:$B$79,A27,Features!$L$2:$L$79,"&lt;&gt;")</f>
+        <f>COUNTIFS(Features!$B$2:$B$79,A27,Features!$N$2:$N$79,"Done")</f>
+        <v>2</v>
+      </c>
+      <c r="E27" s="20">
+        <f t="shared" si="0"/>
+        <v>0.285714285714286</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="9">
+        <f>COUNTIF(Features!$B$2:$B$79,A28)</f>
+        <v>3</v>
+      </c>
+      <c r="D28" s="9">
+        <f>COUNTIFS(Features!$B$2:$B$79,A28,Features!$N$2:$N$79,"Done")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E28" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="F28" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="9">
-        <f>COUNTIF(Features!$B$2:$B$79,A28)</f>
-        <v>5</v>
-      </c>
-      <c r="D28" s="9">
-        <f>COUNTIFS(Features!$B$2:$B$79,A28,Features!$L$2:$L$79,"&lt;&gt;")</f>
+      <c r="B29" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="9">
+        <f>COUNTIF(Features!$B$2:$B$79,A29)</f>
+        <v>7</v>
+      </c>
+      <c r="D29" s="9">
+        <f>COUNTIFS(Features!$B$2:$B$79,A29,Features!$N$2:$N$79,"Done")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="18">
+      <c r="E29" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B29" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="C29" s="9">
-        <f>COUNTIF(Features!$B$2:$B$79,A29)</f>
-        <v>3</v>
-      </c>
-      <c r="D29" s="9">
-        <f>COUNTIFS(Features!$B$2:$B$79,A29,Features!$L$2:$L$79,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -3936,54 +4049,100 @@
       </c>
       <c r="C30" s="9">
         <f>COUNTIF(Features!$B$2:$B$79,A30)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D30" s="9">
-        <f>COUNTIFS(Features!$B$2:$B$79,A30,Features!$L$2:$L$79,"&lt;&gt;")</f>
+        <f>COUNTIFS(Features!$B$2:$B$79,A30,Features!$N$2:$N$79,"Done")</f>
         <v>0</v>
       </c>
-      <c r="E30" s="18">
+      <c r="E30" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F30" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="8" t="s">
+      <c r="B31" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="C31" s="9">
+        <f>COUNTIF(Features!$B$2:$B$79,A31)</f>
+        <v>3</v>
+      </c>
+      <c r="D31" s="9">
+        <f>COUNTIFS(Features!$B$2:$B$79,A31,Features!$N$2:$N$79,"Done")</f>
+        <v>3</v>
+      </c>
+      <c r="E31" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="2">
-        <f>SUM(C20:C30)</f>
-        <v>78</v>
-      </c>
-      <c r="D31" s="2">
-        <f>SUM(D20:D30)</f>
+      <c r="B32" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="9">
+        <f>COUNTIF(Features!$B$2:$B$79,A32)</f>
+        <v>3</v>
+      </c>
+      <c r="D32" s="9">
+        <f>COUNTIFS(Features!$B$2:$B$79,A32,Features!$N$2:$N$79,"Done")</f>
         <v>0</v>
       </c>
-      <c r="E31" s="19">
+      <c r="E32" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F31" s="8" t="s">
-        <v>29</v>
+      <c r="F32" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" s="2">
+        <f>SUM(C22:C32)</f>
+        <v>78</v>
+      </c>
+      <c r="D33" s="2">
+        <f>SUM(D22:D32)</f>
+        <v>37</v>
+      </c>
+      <c r="E33" s="21">
+        <f t="shared" si="0"/>
+        <v>0.474358974358974</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A17:F17"/>
   </mergeCells>
-  <conditionalFormatting sqref="E20:E31">
+  <conditionalFormatting sqref="E22:E33">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>E20=1</formula>
+      <formula>E22=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3997,7 +4156,445 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" spans="1:9">
+      <c r="A1" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="16">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="4" ht="15.6" spans="1:9">
+      <c r="A4" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" ht="26.4" spans="1:9">
+      <c r="A6" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="12">
+        <f>$B$2</f>
+        <v>46272</v>
+      </c>
+      <c r="C6" s="18">
+        <v>46308</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="9">
+        <f>COUNTIF(Features!$L$2:$L$79,1)</f>
+        <v>37</v>
+      </c>
+      <c r="G6" s="9">
+        <f>COUNTIFS(Features!$L$2:$L$79,1,Features!$N$2:$N$79,"Done")</f>
+        <v>37</v>
+      </c>
+      <c r="H6" s="9">
+        <f>COUNTIFS(Features!$L$2:$L$79,1,Features!$N$2:$N$79,"Processing")</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="9">
+        <f>COUNTIFS(Features!$L$2:$L$79,1,Features!$N$2:$N$79,"Not Start")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="12">
+        <f>C6+1</f>
+        <v>46309</v>
+      </c>
+      <c r="C7" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="9">
+        <f>COUNTIF(Features!$L$2:$L$79,2)</f>
+        <v>24</v>
+      </c>
+      <c r="G7" s="9">
+        <f>COUNTIFS(Features!$L$2:$L$79,2,Features!$N$2:$N$79,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
+        <f>COUNTIFS(Features!$L$2:$L$79,2,Features!$N$2:$N$79,"Processing")</f>
+        <v>24</v>
+      </c>
+      <c r="I7" s="9">
+        <f>COUNTIFS(Features!$L$2:$L$79,2,Features!$N$2:$N$79,"Not Start")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="12">
+        <f>C7+1</f>
+        <v>46317</v>
+      </c>
+      <c r="C8" s="18">
+        <v>46322</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="9">
+        <f>COUNTIF(Features!$L$2:$L$79,3)</f>
+        <v>17</v>
+      </c>
+      <c r="G8" s="9">
+        <f>COUNTIFS(Features!$L$2:$L$79,3,Features!$N$2:$N$79,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <f>COUNTIFS(Features!$L$2:$L$79,3,Features!$N$2:$N$79,"Processing")</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="9">
+        <f>COUNTIFS(Features!$L$2:$L$79,3,Features!$N$2:$N$79,"Not Start")</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="19">
+        <f>B6</f>
+        <v>46272</v>
+      </c>
+      <c r="C9" s="19">
+        <f>C8</f>
+        <v>46322</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="2">
+        <f>SUM(F6:F8)</f>
+        <v>78</v>
+      </c>
+      <c r="G9" s="2">
+        <f>SUM(G6:G8)</f>
+        <v>37</v>
+      </c>
+      <c r="H9" s="2">
+        <f>SUM(H6:H8)</f>
+        <v>24</v>
+      </c>
+      <c r="I9" s="2">
+        <f>SUM(I6:I8)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" ht="15.6" spans="1:9">
+      <c r="A11" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" ht="26.4" spans="1:9">
+      <c r="A12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="9">
+        <f>COUNTIF(Features!$O$2:$O$79,A13)</f>
+        <v>17</v>
+      </c>
+      <c r="D13" s="20">
+        <f t="shared" ref="D13:D18" si="0">IF(C13=0,0,F13/C13)</f>
+        <v>0.529411764705882</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="9">
+        <f>COUNTIFS(Features!$O$2:$O$79,A13,Features!$N$2:$N$79,"Done")</f>
+        <v>9</v>
+      </c>
+      <c r="G13" s="9">
+        <f>COUNTIFS(Features!$O$2:$O$79,A13,Features!$N$2:$N$79,"Processing")</f>
+        <v>3</v>
+      </c>
+      <c r="H13" s="9">
+        <f>COUNTIFS(Features!$O$2:$O$79,A13,Features!$N$2:$N$79,"Not Start")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="9">
+        <f>COUNTIF(Features!$O$2:$O$79,A14)</f>
+        <v>15</v>
+      </c>
+      <c r="D14" s="20">
+        <f t="shared" si="0"/>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="9">
+        <f>COUNTIFS(Features!$O$2:$O$79,A14,Features!$N$2:$N$79,"Done")</f>
+        <v>5</v>
+      </c>
+      <c r="G14" s="9">
+        <f>COUNTIFS(Features!$O$2:$O$79,A14,Features!$N$2:$N$79,"Processing")</f>
+        <v>6</v>
+      </c>
+      <c r="H14" s="9">
+        <f>COUNTIFS(Features!$O$2:$O$79,A14,Features!$N$2:$N$79,"Not Start")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="9">
+        <f>COUNTIF(Features!$O$2:$O$79,A15)</f>
+        <v>21</v>
+      </c>
+      <c r="D15" s="20">
+        <f t="shared" si="0"/>
+        <v>0.619047619047619</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="9">
+        <f>COUNTIFS(Features!$O$2:$O$79,A15,Features!$N$2:$N$79,"Done")</f>
+        <v>13</v>
+      </c>
+      <c r="G15" s="9">
+        <f>COUNTIFS(Features!$O$2:$O$79,A15,Features!$N$2:$N$79,"Processing")</f>
+        <v>5</v>
+      </c>
+      <c r="H15" s="9">
+        <f>COUNTIFS(Features!$O$2:$O$79,A15,Features!$N$2:$N$79,"Not Start")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="9">
+        <f>COUNTIF(Features!$O$2:$O$79,A16)</f>
+        <v>12</v>
+      </c>
+      <c r="D16" s="20">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" s="9">
+        <f>COUNTIFS(Features!$O$2:$O$79,A16,Features!$N$2:$N$79,"Done")</f>
+        <v>3</v>
+      </c>
+      <c r="G16" s="9">
+        <f>COUNTIFS(Features!$O$2:$O$79,A16,Features!$N$2:$N$79,"Processing")</f>
+        <v>4</v>
+      </c>
+      <c r="H16" s="9">
+        <f>COUNTIFS(Features!$O$2:$O$79,A16,Features!$N$2:$N$79,"Not Start")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="9">
+        <f>COUNTIF(Features!$O$2:$O$79,A17)</f>
+        <v>13</v>
+      </c>
+      <c r="D17" s="20">
+        <f t="shared" si="0"/>
+        <v>0.538461538461538</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" s="9">
+        <f>COUNTIFS(Features!$O$2:$O$79,A17,Features!$N$2:$N$79,"Done")</f>
+        <v>7</v>
+      </c>
+      <c r="G17" s="9">
+        <f>COUNTIFS(Features!$O$2:$O$79,A17,Features!$N$2:$N$79,"Processing")</f>
+        <v>6</v>
+      </c>
+      <c r="H17" s="9">
+        <f>COUNTIFS(Features!$O$2:$O$79,A17,Features!$N$2:$N$79,"Not Start")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2">
+        <f>SUM(C13:C17)</f>
+        <v>78</v>
+      </c>
+      <c r="D18" s="21">
+        <f t="shared" si="0"/>
+        <v>0.474358974358974</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="2">
+        <f>SUM(F13:F17)</f>
+        <v>37</v>
+      </c>
+      <c r="G18" s="2">
+        <f>SUM(G13:G17)</f>
+        <v>24</v>
+      </c>
+      <c r="H18" s="2">
+        <f>SUM(H13:H17)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="7" t="str">
+        <f>IF(C18=COUNTA(Features!$C$2:$C$79),"All features assigned","Unassigned features: "&amp;(COUNTA(Features!$C$2:$C$79)-C18))</f>
+        <v>All features assigned</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D6:D8">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"Done"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"Processing"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>"Not Start"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" fitToHeight="0" orientation="landscape"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -4011,2870 +4608,3761 @@
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:12">
+    <row r="1" ht="30" customHeight="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="2" ht="39.6" spans="1:12">
+      <c r="O1" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" ht="39.6" spans="1:15">
       <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L2" s="12"/>
-    </row>
-    <row r="3" ht="39.6" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L2" s="9">
+        <v>1</v>
+      </c>
+      <c r="M2" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" ht="39.6" spans="1:15">
       <c r="A3" s="9">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="E3" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="L3" s="9">
+        <v>1</v>
+      </c>
+      <c r="M3" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L3" s="12"/>
-    </row>
-    <row r="4" ht="26.4" spans="1:12">
+    </row>
+    <row r="4" ht="26.4" spans="1:15">
       <c r="A4" s="9">
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L4" s="12"/>
-    </row>
-    <row r="5" ht="39.6" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L4" s="9">
+        <v>1</v>
+      </c>
+      <c r="M4" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" ht="39.6" spans="1:15">
       <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L5" s="12"/>
-    </row>
-    <row r="6" ht="26.4" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L5" s="9">
+        <v>1</v>
+      </c>
+      <c r="M5" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" ht="26.4" spans="1:15">
       <c r="A6" s="9">
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L6" s="12"/>
-    </row>
-    <row r="7" ht="39.6" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L6" s="9">
+        <v>1</v>
+      </c>
+      <c r="M6" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" ht="39.6" spans="1:15">
       <c r="A7" s="9">
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L7" s="12"/>
-    </row>
-    <row r="8" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L7" s="9">
+        <v>1</v>
+      </c>
+      <c r="M7" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" ht="26.4" spans="1:15">
       <c r="A8" s="9">
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K8" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L8" s="12"/>
-    </row>
-    <row r="9" ht="26.4" spans="1:12">
+      <c r="L8" s="9">
+        <v>1</v>
+      </c>
+      <c r="M8" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" ht="26.4" spans="1:15">
       <c r="A9" s="9">
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L9" s="12"/>
-    </row>
-    <row r="10" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L9" s="9">
+        <v>1</v>
+      </c>
+      <c r="M9" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" ht="26.4" spans="1:15">
       <c r="A10" s="9">
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L10" s="12"/>
-    </row>
-    <row r="11" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L10" s="9">
+        <v>1</v>
+      </c>
+      <c r="M10" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" ht="26.4" spans="1:15">
       <c r="A11" s="9">
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L11" s="12"/>
-    </row>
-    <row r="12" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L11" s="9">
+        <v>2</v>
+      </c>
+      <c r="M11" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O11" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" ht="26.4" spans="1:15">
       <c r="A12" s="9">
         <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L12" s="12"/>
-    </row>
-    <row r="13" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L12" s="9">
+        <v>2</v>
+      </c>
+      <c r="M12" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O12" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" ht="26.4" spans="1:15">
       <c r="A13" s="9">
         <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L13" s="12"/>
-    </row>
-    <row r="14" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L13" s="9">
+        <v>2</v>
+      </c>
+      <c r="M13" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" ht="26.4" spans="1:15">
       <c r="A14" s="9">
         <v>13</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L14" s="12"/>
-    </row>
-    <row r="15" ht="26.4" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L14" s="9">
+        <v>3</v>
+      </c>
+      <c r="M14" s="12">
+        <v>46322</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" ht="26.4" spans="1:15">
       <c r="A15" s="9">
         <v>14</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>162</v>
+        <v>199</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L15" s="12"/>
-    </row>
-    <row r="16" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L15" s="9">
+        <v>3</v>
+      </c>
+      <c r="M15" s="12">
+        <v>46322</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O15" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" ht="26.4" spans="1:15">
       <c r="A16" s="9">
         <v>15</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>163</v>
+        <v>200</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>164</v>
+        <v>201</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>165</v>
+        <v>202</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>166</v>
+        <v>203</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L16" s="12"/>
-    </row>
-    <row r="17" ht="26.4" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L16" s="9">
+        <v>3</v>
+      </c>
+      <c r="M16" s="12">
+        <v>46322</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O16" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" ht="26.4" spans="1:15">
       <c r="A17" s="9">
         <v>16</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>169</v>
+        <v>206</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>171</v>
+        <v>208</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L17" s="12"/>
-    </row>
-    <row r="18" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L17" s="9">
+        <v>3</v>
+      </c>
+      <c r="M17" s="12">
+        <v>46322</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O17" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" ht="26.4" spans="1:15">
       <c r="A18" s="9">
         <v>17</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>180</v>
+        <v>217</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L18" s="12"/>
-    </row>
-    <row r="19" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L18" s="9">
+        <v>3</v>
+      </c>
+      <c r="M18" s="12">
+        <v>46322</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O18" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" ht="26.4" spans="1:15">
       <c r="A19" s="9">
         <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>183</v>
+        <v>220</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>184</v>
+        <v>221</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L19" s="12"/>
-    </row>
-    <row r="20" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L19" s="9">
+        <v>1</v>
+      </c>
+      <c r="M19" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O19" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" ht="26.4" spans="1:15">
       <c r="A20" s="9">
         <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L20" s="12"/>
-    </row>
-    <row r="21" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L20" s="9">
+        <v>1</v>
+      </c>
+      <c r="M20" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O20" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" ht="26.4" spans="1:15">
       <c r="A21" s="9">
         <v>20</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>195</v>
+        <v>232</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>196</v>
+        <v>233</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>198</v>
+        <v>235</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L21" s="12"/>
-    </row>
-    <row r="22" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L21" s="9">
+        <v>1</v>
+      </c>
+      <c r="M21" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O21" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" ht="26.4" spans="1:15">
       <c r="A22" s="9">
         <v>21</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>201</v>
+        <v>238</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>203</v>
+        <v>240</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>204</v>
+        <v>241</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>205</v>
+        <v>242</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L22" s="12"/>
-    </row>
-    <row r="23" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L22" s="9">
+        <v>1</v>
+      </c>
+      <c r="M22" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O22" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" ht="26.4" spans="1:15">
       <c r="A23" s="9">
         <v>22</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>206</v>
+        <v>243</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>207</v>
+        <v>244</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>208</v>
+        <v>245</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L23" s="12"/>
-    </row>
-    <row r="24" ht="26.4" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L23" s="9">
+        <v>1</v>
+      </c>
+      <c r="M23" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O23" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" ht="26.4" spans="1:15">
       <c r="A24" s="9">
         <v>23</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>215</v>
+        <v>252</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>216</v>
+        <v>253</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L24" s="12"/>
-    </row>
-    <row r="25" ht="26.4" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L24" s="9">
+        <v>1</v>
+      </c>
+      <c r="M24" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O24" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" ht="26.4" spans="1:15">
       <c r="A25" s="9">
         <v>24</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>219</v>
+        <v>256</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>221</v>
+        <v>258</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L25" s="12"/>
-    </row>
-    <row r="26" ht="26.4" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L25" s="9">
+        <v>1</v>
+      </c>
+      <c r="M25" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O25" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" ht="26.4" spans="1:15">
       <c r="A26" s="9">
         <v>25</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>222</v>
+        <v>259</v>
       </c>
       <c r="D26" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>205</v>
+        <v>242</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L26" s="12"/>
-    </row>
-    <row r="27" ht="26.4" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L26" s="9">
+        <v>1</v>
+      </c>
+      <c r="M26" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O26" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" ht="26.4" spans="1:15">
       <c r="A27" s="9">
         <v>26</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>227</v>
+        <v>264</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>229</v>
+        <v>266</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>230</v>
+        <v>267</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>231</v>
+        <v>268</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>232</v>
+        <v>269</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L27" s="12"/>
-    </row>
-    <row r="28" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L27" s="9">
+        <v>1</v>
+      </c>
+      <c r="M27" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O27" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" ht="26.4" spans="1:15">
       <c r="A28" s="9">
         <v>27</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>233</v>
+        <v>270</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>234</v>
+        <v>271</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>235</v>
+        <v>272</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>236</v>
+        <v>273</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>237</v>
+        <v>274</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L28" s="12"/>
-    </row>
-    <row r="29" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L28" s="9">
+        <v>1</v>
+      </c>
+      <c r="M28" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O28" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" ht="26.4" spans="1:15">
       <c r="A29" s="9">
         <v>28</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>239</v>
+        <v>276</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>241</v>
+        <v>278</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>242</v>
+        <v>279</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>243</v>
+        <v>280</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>244</v>
+        <v>281</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L29" s="12"/>
-    </row>
-    <row r="30" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L29" s="9">
+        <v>1</v>
+      </c>
+      <c r="M29" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O29" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" ht="26.4" spans="1:15">
       <c r="A30" s="9">
         <v>29</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>245</v>
+        <v>282</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>246</v>
+        <v>283</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>247</v>
+        <v>284</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>248</v>
+        <v>285</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>249</v>
+        <v>286</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>250</v>
+        <v>287</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L30" s="12"/>
-    </row>
-    <row r="31" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L30" s="9">
+        <v>1</v>
+      </c>
+      <c r="M30" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N30" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O30" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" ht="26.4" spans="1:15">
       <c r="A31" s="9">
         <v>30</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>251</v>
+        <v>288</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>254</v>
+        <v>291</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>256</v>
+        <v>293</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L31" s="12"/>
-    </row>
-    <row r="32" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L31" s="9">
+        <v>1</v>
+      </c>
+      <c r="M31" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N31" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O31" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" ht="26.4" spans="1:15">
       <c r="A32" s="9">
         <v>31</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>257</v>
+        <v>294</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>258</v>
+        <v>295</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>259</v>
+        <v>296</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>260</v>
+        <v>297</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>262</v>
+        <v>299</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L32" s="12"/>
-    </row>
-    <row r="33" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L32" s="9">
+        <v>2</v>
+      </c>
+      <c r="M32" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N32" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O32" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" ht="26.4" spans="1:15">
       <c r="A33" s="9">
         <v>32</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>263</v>
+        <v>300</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>265</v>
+        <v>302</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>268</v>
+        <v>305</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L33" s="12"/>
-    </row>
-    <row r="34" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L33" s="9">
+        <v>2</v>
+      </c>
+      <c r="M33" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N33" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O33" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" ht="26.4" spans="1:15">
       <c r="A34" s="9">
         <v>33</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>269</v>
+        <v>306</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>272</v>
+        <v>309</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>273</v>
+        <v>310</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L34" s="12"/>
-    </row>
-    <row r="35" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L34" s="9">
+        <v>2</v>
+      </c>
+      <c r="M34" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N34" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O34" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" ht="26.4" spans="1:15">
       <c r="A35" s="9">
         <v>34</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>275</v>
+        <v>312</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>276</v>
+        <v>313</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>277</v>
+        <v>314</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>279</v>
+        <v>316</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>280</v>
+        <v>317</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L35" s="12"/>
-    </row>
-    <row r="36" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L35" s="9">
+        <v>3</v>
+      </c>
+      <c r="M35" s="12">
+        <v>46322</v>
+      </c>
+      <c r="N35" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O35" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" ht="26.4" spans="1:15">
       <c r="A36" s="9">
         <v>35</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>281</v>
+        <v>318</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>282</v>
+        <v>319</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>283</v>
+        <v>320</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>284</v>
+        <v>321</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>285</v>
+        <v>322</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>286</v>
+        <v>323</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L36" s="12"/>
-    </row>
-    <row r="37" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L36" s="9">
+        <v>3</v>
+      </c>
+      <c r="M36" s="12">
+        <v>46322</v>
+      </c>
+      <c r="N36" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O36" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" ht="26.4" spans="1:15">
       <c r="A37" s="9">
         <v>36</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>287</v>
+        <v>324</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>288</v>
+        <v>325</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>289</v>
+        <v>326</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>291</v>
+        <v>328</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>280</v>
+        <v>317</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L37" s="12"/>
-    </row>
-    <row r="38" ht="26.4" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L37" s="9">
+        <v>3</v>
+      </c>
+      <c r="M37" s="12">
+        <v>46322</v>
+      </c>
+      <c r="N37" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O37" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" ht="26.4" spans="1:15">
       <c r="A38" s="9">
         <v>37</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>293</v>
+        <v>330</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>294</v>
+        <v>331</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>295</v>
+        <v>332</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>296</v>
+        <v>333</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>286</v>
+        <v>323</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L38" s="12"/>
-    </row>
-    <row r="39" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L38" s="9">
+        <v>3</v>
+      </c>
+      <c r="M38" s="12">
+        <v>46322</v>
+      </c>
+      <c r="N38" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O38" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" ht="26.4" spans="1:15">
       <c r="A39" s="9">
         <v>38</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>297</v>
+        <v>334</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>298</v>
+        <v>335</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>299</v>
+        <v>336</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>300</v>
+        <v>337</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>301</v>
+        <v>338</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>303</v>
+        <v>340</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L39" s="12"/>
-    </row>
-    <row r="40" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L39" s="9">
+        <v>1</v>
+      </c>
+      <c r="M39" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N39" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O39" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" ht="26.4" spans="1:15">
       <c r="A40" s="9">
         <v>39</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>304</v>
+        <v>341</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>305</v>
+        <v>342</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>306</v>
+        <v>343</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>307</v>
+        <v>344</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>301</v>
+        <v>338</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>308</v>
+        <v>345</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>310</v>
+        <v>347</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L40" s="12"/>
-    </row>
-    <row r="41" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L40" s="9">
+        <v>1</v>
+      </c>
+      <c r="M40" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N40" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O40" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
       <c r="A41" s="9">
         <v>40</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>312</v>
+        <v>349</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>313</v>
+        <v>350</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>314</v>
+        <v>351</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>301</v>
+        <v>338</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>315</v>
+        <v>352</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>316</v>
+        <v>353</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>317</v>
+        <v>354</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L41" s="12"/>
-    </row>
-    <row r="42" ht="36" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L41" s="9">
+        <v>1</v>
+      </c>
+      <c r="M41" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N41" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O41" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42" ht="36" spans="1:15">
       <c r="A42" s="9">
         <v>41</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>318</v>
+        <v>355</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>319</v>
+        <v>356</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>320</v>
+        <v>357</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>321</v>
+        <v>358</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>301</v>
+        <v>338</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>322</v>
+        <v>359</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>323</v>
+        <v>360</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>317</v>
+        <v>354</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L42" s="12"/>
-    </row>
-    <row r="43" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L42" s="9">
+        <v>1</v>
+      </c>
+      <c r="M42" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N42" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O42" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="43" ht="26.4" spans="1:15">
       <c r="A43" s="9">
         <v>42</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>324</v>
+        <v>361</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>325</v>
+        <v>362</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>326</v>
+        <v>363</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>327</v>
+        <v>364</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>301</v>
+        <v>338</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>328</v>
+        <v>365</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>329</v>
+        <v>366</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="K43" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L43" s="12"/>
-    </row>
-    <row r="44" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L43" s="9">
+        <v>1</v>
+      </c>
+      <c r="M43" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N43" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O43" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" s="9">
         <v>43</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>331</v>
+        <v>368</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>332</v>
+        <v>369</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>333</v>
+        <v>370</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>335</v>
+        <v>372</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>337</v>
+        <v>374</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L44" s="12"/>
-    </row>
-    <row r="45" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L44" s="9">
+        <v>2</v>
+      </c>
+      <c r="M44" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N44" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O44" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" ht="26.4" spans="1:15">
       <c r="A45" s="9">
         <v>44</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>338</v>
+        <v>375</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>339</v>
+        <v>376</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>340</v>
+        <v>377</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>341</v>
+        <v>378</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>342</v>
+        <v>379</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>343</v>
+        <v>380</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L45" s="12"/>
-    </row>
-    <row r="46" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L45" s="9">
+        <v>2</v>
+      </c>
+      <c r="M45" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N45" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O45" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="46" ht="26.4" spans="1:15">
       <c r="A46" s="9">
         <v>45</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>344</v>
+        <v>381</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>345</v>
+        <v>382</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>346</v>
+        <v>383</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>347</v>
+        <v>384</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>348</v>
+        <v>385</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>349</v>
+        <v>386</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L46" s="12"/>
-    </row>
-    <row r="47" ht="26.4" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L46" s="9">
+        <v>2</v>
+      </c>
+      <c r="M46" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N46" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O46" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" ht="26.4" spans="1:15">
       <c r="A47" s="9">
         <v>46</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>350</v>
+        <v>387</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>351</v>
+        <v>388</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>352</v>
+        <v>389</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>353</v>
+        <v>390</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>354</v>
+        <v>391</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>356</v>
+        <v>393</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L47" s="12"/>
-    </row>
-    <row r="48" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L47" s="9">
+        <v>1</v>
+      </c>
+      <c r="M47" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N47" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O47" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" ht="26.4" spans="1:15">
       <c r="A48" s="9">
         <v>47</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>357</v>
+        <v>394</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>358</v>
+        <v>395</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>359</v>
+        <v>396</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>360</v>
+        <v>397</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>361</v>
+        <v>398</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>362</v>
+        <v>399</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L48" s="12"/>
-    </row>
-    <row r="49" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L48" s="9">
+        <v>1</v>
+      </c>
+      <c r="M48" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N48" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O48" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
       <c r="A49" s="9">
         <v>48</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>363</v>
+        <v>400</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>364</v>
+        <v>401</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>365</v>
+        <v>402</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>366</v>
+        <v>403</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>367</v>
+        <v>404</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L49" s="12"/>
-    </row>
-    <row r="50" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L49" s="9">
+        <v>1</v>
+      </c>
+      <c r="M49" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N49" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O49" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
       <c r="A50" s="9">
         <v>49</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>369</v>
+        <v>406</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>372</v>
+        <v>409</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>373</v>
+        <v>410</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>374</v>
+        <v>411</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L50" s="12"/>
-    </row>
-    <row r="51" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L50" s="9">
+        <v>1</v>
+      </c>
+      <c r="M50" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N50" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O50" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
       <c r="A51" s="9">
         <v>50</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>375</v>
+        <v>412</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>377</v>
+        <v>414</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>374</v>
+        <v>411</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L51" s="12"/>
-    </row>
-    <row r="52" ht="39.6" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L51" s="9">
+        <v>1</v>
+      </c>
+      <c r="M51" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N51" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O51" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="52" ht="39.6" spans="1:15">
       <c r="A52" s="9">
         <v>51</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>380</v>
+        <v>417</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>381</v>
+        <v>418</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>382</v>
+        <v>419</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>383</v>
+        <v>420</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>384</v>
+        <v>421</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>385</v>
+        <v>422</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>386</v>
+        <v>423</v>
       </c>
       <c r="K52" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L52" s="12"/>
-    </row>
-    <row r="53" ht="52.8" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L52" s="9">
+        <v>1</v>
+      </c>
+      <c r="M52" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N52" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O52" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" ht="52.8" spans="1:15">
       <c r="A53" s="9">
         <v>52</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>387</v>
+        <v>424</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>388</v>
+        <v>425</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>389</v>
+        <v>426</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>390</v>
+        <v>427</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>391</v>
+        <v>428</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>392</v>
+        <v>429</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>393</v>
+        <v>430</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L53" s="12"/>
-    </row>
-    <row r="54" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L53" s="9">
+        <v>1</v>
+      </c>
+      <c r="M53" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N53" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O53" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54" s="9">
         <v>53</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>394</v>
+        <v>431</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>395</v>
+        <v>432</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>396</v>
+        <v>433</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>397</v>
+        <v>434</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>398</v>
+        <v>435</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>399</v>
+        <v>436</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>400</v>
+        <v>437</v>
       </c>
       <c r="K54" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L54" s="12"/>
-    </row>
-    <row r="55" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L54" s="9">
+        <v>2</v>
+      </c>
+      <c r="M54" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N54" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O54" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" ht="26.4" spans="1:15">
       <c r="A55" s="9">
         <v>54</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>401</v>
+        <v>438</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>402</v>
+        <v>439</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>403</v>
+        <v>440</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>404</v>
+        <v>441</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>405</v>
+        <v>442</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>406</v>
+        <v>443</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>407</v>
+        <v>444</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L55" s="12"/>
-    </row>
-    <row r="56" ht="39.6" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L55" s="9">
+        <v>2</v>
+      </c>
+      <c r="M55" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N55" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O55" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56" ht="39.6" spans="1:15">
       <c r="A56" s="9">
         <v>55</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>408</v>
+        <v>445</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>410</v>
+        <v>447</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>411</v>
+        <v>448</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>412</v>
+        <v>449</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>406</v>
+        <v>443</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>413</v>
+        <v>450</v>
       </c>
       <c r="K56" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L56" s="12"/>
-    </row>
-    <row r="57" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L56" s="9">
+        <v>2</v>
+      </c>
+      <c r="M56" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N56" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O56" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
       <c r="A57" s="9">
         <v>56</v>
       </c>
       <c r="B57" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="G57" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>416</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="H57" s="11" t="s">
-        <v>418</v>
+        <v>455</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>419</v>
+        <v>456</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>420</v>
+        <v>457</v>
       </c>
       <c r="K57" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L57" s="12"/>
-    </row>
-    <row r="58" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L57" s="9">
+        <v>2</v>
+      </c>
+      <c r="M57" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N57" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O57" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="58" ht="26.4" spans="1:15">
       <c r="A58" s="9">
         <v>57</v>
       </c>
       <c r="B58" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="G58" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>423</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="H58" s="11" t="s">
-        <v>425</v>
+        <v>462</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>419</v>
+        <v>456</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>426</v>
+        <v>463</v>
       </c>
       <c r="K58" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L58" s="12"/>
-    </row>
-    <row r="59" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L58" s="9">
+        <v>2</v>
+      </c>
+      <c r="M58" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N58" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O58" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="59" ht="26.4" spans="1:15">
       <c r="A59" s="9">
         <v>58</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>427</v>
+        <v>464</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>428</v>
+        <v>465</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>429</v>
+        <v>466</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>430</v>
+        <v>467</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>431</v>
+        <v>468</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>406</v>
+        <v>443</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>432</v>
+        <v>469</v>
       </c>
       <c r="K59" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L59" s="12"/>
-    </row>
-    <row r="60" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L59" s="9">
+        <v>2</v>
+      </c>
+      <c r="M59" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N59" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O59" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="60" ht="26.4" spans="1:15">
       <c r="A60" s="9">
         <v>59</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>433</v>
+        <v>470</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>434</v>
+        <v>471</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>435</v>
+        <v>472</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>436</v>
+        <v>473</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>437</v>
+        <v>474</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>439</v>
+        <v>476</v>
       </c>
       <c r="K60" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L60" s="12"/>
-    </row>
-    <row r="61" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L60" s="9">
+        <v>2</v>
+      </c>
+      <c r="M60" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N60" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O60" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="61" ht="26.4" spans="1:15">
       <c r="A61" s="9">
         <v>60</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>440</v>
+        <v>477</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>441</v>
+        <v>478</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>442</v>
+        <v>479</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>443</v>
+        <v>480</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>444</v>
+        <v>481</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>419</v>
+        <v>456</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>445</v>
+        <v>482</v>
       </c>
       <c r="K61" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L61" s="12"/>
-    </row>
-    <row r="62" ht="26.4" spans="1:12">
+        <v>113</v>
+      </c>
+      <c r="L61" s="9">
+        <v>2</v>
+      </c>
+      <c r="M61" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N61" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O61" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62" ht="26.4" spans="1:15">
       <c r="A62" s="9">
         <v>61</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>446</v>
+        <v>483</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>447</v>
+        <v>484</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>449</v>
+        <v>486</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>450</v>
+        <v>487</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>451</v>
+        <v>488</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
       <c r="K62" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L62" s="12"/>
-    </row>
-    <row r="63" ht="24" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L62" s="9">
+        <v>2</v>
+      </c>
+      <c r="M62" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N62" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O62" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="63" ht="24" spans="1:15">
       <c r="A63" s="9">
         <v>62</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>453</v>
+        <v>490</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>454</v>
+        <v>491</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>455</v>
+        <v>492</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>456</v>
+        <v>493</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>457</v>
+        <v>494</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>451</v>
+        <v>488</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>458</v>
+        <v>495</v>
       </c>
       <c r="K63" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L63" s="12"/>
-    </row>
-    <row r="64" ht="26.4" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L63" s="9">
+        <v>2</v>
+      </c>
+      <c r="M63" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N63" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O63" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="64" ht="26.4" spans="1:15">
       <c r="A64" s="9">
         <v>63</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>459</v>
+        <v>496</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>460</v>
+        <v>497</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>461</v>
+        <v>498</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>462</v>
+        <v>499</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>451</v>
+        <v>488</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>464</v>
+        <v>501</v>
       </c>
       <c r="K64" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L64" s="12"/>
-    </row>
-    <row r="65" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L64" s="9">
+        <v>2</v>
+      </c>
+      <c r="M64" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N64" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O64" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
       <c r="A65" s="9">
         <v>64</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>466</v>
+        <v>503</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>467</v>
+        <v>504</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>468</v>
+        <v>505</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>469</v>
+        <v>506</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>451</v>
+        <v>488</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>470</v>
+        <v>507</v>
       </c>
       <c r="K65" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L65" s="12"/>
-    </row>
-    <row r="66" ht="26.4" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L65" s="9">
+        <v>2</v>
+      </c>
+      <c r="M65" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N65" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O65" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="66" ht="26.4" spans="1:15">
       <c r="A66" s="9">
         <v>65</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>471</v>
+        <v>508</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>472</v>
+        <v>509</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>473</v>
+        <v>510</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>474</v>
+        <v>511</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>475</v>
+        <v>512</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>385</v>
+        <v>422</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>476</v>
+        <v>513</v>
       </c>
       <c r="K66" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L66" s="12"/>
-    </row>
-    <row r="67" ht="26.4" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L66" s="9">
+        <v>2</v>
+      </c>
+      <c r="M66" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N66" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O66" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" ht="26.4" spans="1:15">
       <c r="A67" s="9">
         <v>66</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>477</v>
+        <v>514</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>478</v>
+        <v>515</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>479</v>
+        <v>516</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>480</v>
+        <v>517</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>481</v>
+        <v>518</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>385</v>
+        <v>422</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>482</v>
+        <v>519</v>
       </c>
       <c r="K67" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L67" s="12"/>
-    </row>
-    <row r="68" ht="26.4" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L67" s="9">
+        <v>2</v>
+      </c>
+      <c r="M67" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N67" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O67" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68" ht="26.4" spans="1:15">
       <c r="A68" s="9">
         <v>67</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>483</v>
+        <v>520</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>484</v>
+        <v>521</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>485</v>
+        <v>522</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>486</v>
+        <v>523</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>487</v>
+        <v>524</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>385</v>
+        <v>422</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>488</v>
+        <v>525</v>
       </c>
       <c r="K68" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L68" s="12"/>
-    </row>
-    <row r="69" ht="26.4" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L68" s="9">
+        <v>2</v>
+      </c>
+      <c r="M68" s="12">
+        <v>46316</v>
+      </c>
+      <c r="N68" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O68" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" ht="26.4" spans="1:15">
       <c r="A69" s="9">
         <v>68</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>489</v>
+        <v>526</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>490</v>
+        <v>527</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>491</v>
+        <v>528</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>493</v>
+        <v>530</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>494</v>
+        <v>531</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
       <c r="K69" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L69" s="12"/>
-    </row>
-    <row r="70" ht="26.4" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L69" s="9">
+        <v>3</v>
+      </c>
+      <c r="M69" s="12">
+        <v>46322</v>
+      </c>
+      <c r="N69" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O69" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="70" ht="26.4" spans="1:15">
       <c r="A70" s="9">
         <v>69</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>496</v>
+        <v>533</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>497</v>
+        <v>534</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>498</v>
+        <v>535</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>499</v>
+        <v>536</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>500</v>
+        <v>537</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>501</v>
+        <v>538</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="K70" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L70" s="12"/>
-    </row>
-    <row r="71" ht="26.4" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L70" s="9">
+        <v>3</v>
+      </c>
+      <c r="M70" s="12">
+        <v>46322</v>
+      </c>
+      <c r="N70" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O70" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="71" ht="26.4" spans="1:15">
       <c r="A71" s="9">
         <v>70</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>503</v>
+        <v>540</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>504</v>
+        <v>541</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>505</v>
+        <v>542</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>506</v>
+        <v>543</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>507</v>
+        <v>544</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>494</v>
+        <v>531</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>508</v>
+        <v>545</v>
       </c>
       <c r="K71" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L71" s="12"/>
-    </row>
-    <row r="72" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L71" s="9">
+        <v>3</v>
+      </c>
+      <c r="M71" s="12">
+        <v>46322</v>
+      </c>
+      <c r="N71" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O71" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
       <c r="A72" s="9">
         <v>71</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>509</v>
+        <v>546</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>510</v>
+        <v>547</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>511</v>
+        <v>548</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>512</v>
+        <v>549</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>513</v>
+        <v>550</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>494</v>
+        <v>531</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>514</v>
+        <v>551</v>
       </c>
       <c r="K72" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L72" s="12"/>
-    </row>
-    <row r="73" ht="26.4" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L72" s="9">
+        <v>3</v>
+      </c>
+      <c r="M72" s="12">
+        <v>46322</v>
+      </c>
+      <c r="N72" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O72" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="73" ht="26.4" spans="1:15">
       <c r="A73" s="9">
         <v>72</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>515</v>
+        <v>552</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>516</v>
+        <v>553</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>517</v>
+        <v>554</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>518</v>
+        <v>555</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>520</v>
+        <v>557</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
       <c r="K73" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L73" s="12"/>
-    </row>
-    <row r="74" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L73" s="9">
+        <v>3</v>
+      </c>
+      <c r="M73" s="12">
+        <v>46322</v>
+      </c>
+      <c r="N73" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O73" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
       <c r="A74" s="9">
         <v>73</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>523</v>
+        <v>560</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>524</v>
+        <v>561</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>525</v>
+        <v>562</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>526</v>
+        <v>563</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>527</v>
+        <v>564</v>
       </c>
       <c r="K74" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="L74" s="12"/>
-    </row>
-    <row r="75" spans="1:12">
+        <v>565</v>
+      </c>
+      <c r="L74" s="9">
+        <v>1</v>
+      </c>
+      <c r="M74" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N74" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O74" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
       <c r="A75" s="9">
         <v>74</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>529</v>
+        <v>566</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>530</v>
+        <v>567</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>531</v>
+        <v>568</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>532</v>
+        <v>569</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>533</v>
+        <v>570</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>534</v>
+        <v>571</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>535</v>
+        <v>572</v>
       </c>
       <c r="K75" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="L75" s="12"/>
-    </row>
-    <row r="76" ht="26.4" spans="1:12">
+        <v>565</v>
+      </c>
+      <c r="L75" s="9">
+        <v>1</v>
+      </c>
+      <c r="M75" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N75" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O75" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="76" ht="26.4" spans="1:15">
       <c r="A76" s="9">
         <v>75</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>536</v>
+        <v>573</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>537</v>
+        <v>574</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>538</v>
+        <v>575</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>527</v>
+        <v>564</v>
       </c>
       <c r="K76" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="L76" s="12"/>
-    </row>
-    <row r="77" ht="26.4" spans="1:12">
+        <v>565</v>
+      </c>
+      <c r="L76" s="9">
+        <v>1</v>
+      </c>
+      <c r="M76" s="12">
+        <v>46308</v>
+      </c>
+      <c r="N76" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O76" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="77" ht="26.4" spans="1:15">
       <c r="A77" s="9">
         <v>76</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>542</v>
+        <v>579</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>544</v>
+        <v>581</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>545</v>
+        <v>582</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>546</v>
+        <v>583</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>547</v>
+        <v>584</v>
       </c>
       <c r="K77" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L77" s="12"/>
-    </row>
-    <row r="78" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L77" s="9">
+        <v>3</v>
+      </c>
+      <c r="M77" s="12">
+        <v>46322</v>
+      </c>
+      <c r="N77" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O77" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
       <c r="A78" s="9">
         <v>77</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>548</v>
+        <v>585</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>549</v>
+        <v>586</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>550</v>
+        <v>587</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>551</v>
+        <v>588</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>552</v>
+        <v>589</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>546</v>
+        <v>583</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>547</v>
+        <v>584</v>
       </c>
       <c r="K78" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L78" s="12"/>
-    </row>
-    <row r="79" ht="26.4" spans="1:12">
+        <v>135</v>
+      </c>
+      <c r="L78" s="9">
+        <v>3</v>
+      </c>
+      <c r="M78" s="12">
+        <v>46322</v>
+      </c>
+      <c r="N78" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O78" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="79" ht="26.4" spans="1:15">
       <c r="A79" s="9">
         <v>78</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>553</v>
+        <v>590</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>554</v>
+        <v>591</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>555</v>
+        <v>592</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>557</v>
+        <v>594</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>546</v>
+        <v>583</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>558</v>
+        <v>595</v>
       </c>
       <c r="K79" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L79" s="12"/>
+        <v>135</v>
+      </c>
+      <c r="L79" s="9">
+        <v>3</v>
+      </c>
+      <c r="M79" s="12">
+        <v>46322</v>
+      </c>
+      <c r="N79" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O79" s="13" t="s">
+        <v>85</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L79" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O79" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="K2:K79">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"Must"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"Should"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"Could"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N79">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"Done"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"Processing"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>"Not Start"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" sqref="L2:L79">
+      <formula1>"1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="N2:N79">
+      <formula1>"Done,Processing,Not Start"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="O2:O79">
+      <formula1>'Delivery Plan'!$A$13:$A$17</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="1" fitToHeight="0" orientation="landscape"/>
   <headerFooter/>
@@ -6882,7 +8370,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D5"/>
@@ -6896,72 +8384,72 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>559</v>
+        <v>596</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>560</v>
+        <v>597</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>561</v>
+        <v>598</v>
       </c>
     </row>
     <row r="2" ht="26.4" spans="1:4">
       <c r="A2" s="8" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>562</v>
+        <v>599</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>563</v>
+        <v>600</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>564</v>
+        <v>601</v>
       </c>
     </row>
     <row r="3" ht="26.4" spans="1:4">
       <c r="A3" s="8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>565</v>
+        <v>602</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>566</v>
+        <v>603</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>567</v>
+        <v>604</v>
       </c>
     </row>
     <row r="4" ht="39.6" spans="1:4">
       <c r="A4" s="8" t="s">
-        <v>568</v>
+        <v>605</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>565</v>
+        <v>602</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>569</v>
+        <v>606</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>570</v>
+        <v>607</v>
       </c>
     </row>
     <row r="5" ht="26.4" spans="1:4">
       <c r="A5" s="8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>565</v>
+        <v>602</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>571</v>
+        <v>608</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>572</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>
@@ -6973,7 +8461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E13"/>
@@ -6986,223 +8474,223 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>573</v>
+        <v>610</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>568</v>
+        <v>605</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>574</v>
+        <v>611</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>576</v>
+        <v>613</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>578</v>
+        <v>615</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>579</v>
+        <v>616</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>579</v>
+        <v>616</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>580</v>
+        <v>617</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>581</v>
+        <v>618</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>582</v>
+        <v>619</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>583</v>
+        <v>620</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>442</v>
+        <v>479</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>584</v>
+        <v>621</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>585</v>
+        <v>622</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>586</v>
+        <v>623</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>587</v>
+        <v>624</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>
@@ -7211,7 +8699,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
@@ -7224,387 +8712,387 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>588</v>
+        <v>625</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>568</v>
+        <v>605</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>589</v>
+        <v>626</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>590</v>
+        <v>627</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>593</v>
+        <v>630</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>594</v>
+        <v>631</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>595</v>
+        <v>632</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>596</v>
+        <v>633</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>597</v>
+        <v>634</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>598</v>
+        <v>635</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>599</v>
+        <v>636</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>600</v>
+        <v>637</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>598</v>
+        <v>635</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>601</v>
+        <v>638</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>602</v>
+        <v>639</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>603</v>
+        <v>640</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>604</v>
+        <v>641</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>605</v>
+        <v>642</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>606</v>
+        <v>643</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>607</v>
+        <v>644</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>608</v>
+        <v>645</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>609</v>
+        <v>646</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="3" t="s">
-        <v>610</v>
+        <v>647</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>611</v>
+        <v>648</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
-        <v>520</v>
+        <v>557</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>612</v>
+        <v>649</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3" t="s">
-        <v>451</v>
+        <v>488</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>613</v>
+        <v>650</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>614</v>
+        <v>651</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="3" t="s">
-        <v>615</v>
+        <v>652</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>616</v>
+        <v>653</v>
       </c>
     </row>
   </sheetData>
@@ -7613,7 +9101,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C79"/>
@@ -7626,871 +9114,871 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>617</v>
+        <v>654</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>618</v>
+        <v>655</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>619</v>
+        <v>656</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>620</v>
+        <v>657</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>621</v>
+        <v>658</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>622</v>
+        <v>659</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>624</v>
+        <v>661</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>622</v>
+        <v>659</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>625</v>
+        <v>662</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>626</v>
+        <v>663</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>622</v>
+        <v>659</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>627</v>
+        <v>664</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>628</v>
+        <v>665</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>622</v>
+        <v>659</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>629</v>
+        <v>666</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>630</v>
+        <v>667</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>622</v>
+        <v>659</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>631</v>
+        <v>668</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>632</v>
+        <v>669</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>622</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>633</v>
+        <v>670</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>634</v>
+        <v>671</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>622</v>
+        <v>659</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>635</v>
+        <v>672</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>636</v>
+        <v>673</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>637</v>
+        <v>674</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>638</v>
+        <v>675</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>639</v>
+        <v>676</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>637</v>
+        <v>674</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>640</v>
+        <v>677</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>641</v>
+        <v>678</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>637</v>
+        <v>674</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>642</v>
+        <v>679</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>643</v>
+        <v>680</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>637</v>
+        <v>674</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>644</v>
+        <v>681</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>645</v>
+        <v>682</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>637</v>
+        <v>674</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>646</v>
+        <v>683</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>647</v>
+        <v>684</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>637</v>
+        <v>674</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>648</v>
+        <v>685</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>649</v>
+        <v>686</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>650</v>
+        <v>687</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>216</v>
+        <v>253</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>651</v>
+        <v>688</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>650</v>
+        <v>687</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>652</v>
+        <v>689</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>653</v>
+        <v>690</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>650</v>
+        <v>687</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>654</v>
+        <v>691</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>655</v>
+        <v>692</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>650</v>
+        <v>687</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>656</v>
+        <v>693</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>657</v>
+        <v>694</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>650</v>
+        <v>687</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>286</v>
+        <v>323</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>658</v>
+        <v>695</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>650</v>
+        <v>687</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>659</v>
+        <v>696</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>660</v>
+        <v>697</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>650</v>
+        <v>687</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>650</v>
+        <v>687</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>662</v>
+        <v>699</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>663</v>
+        <v>700</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>664</v>
+        <v>701</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>665</v>
+        <v>702</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>666</v>
+        <v>703</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>669</v>
+        <v>706</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>670</v>
+        <v>707</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>671</v>
+        <v>708</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>672</v>
+        <v>709</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>674</v>
+        <v>711</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>675</v>
+        <v>712</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>374</v>
+        <v>411</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>676</v>
+        <v>713</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>677</v>
+        <v>714</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>678</v>
+        <v>715</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>679</v>
+        <v>716</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>677</v>
+        <v>714</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>680</v>
+        <v>717</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>677</v>
+        <v>714</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>682</v>
+        <v>719</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>683</v>
+        <v>720</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>677</v>
+        <v>714</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>684</v>
+        <v>721</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>677</v>
+        <v>714</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>686</v>
+        <v>723</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>687</v>
+        <v>724</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>677</v>
+        <v>714</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>688</v>
+        <v>725</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>689</v>
+        <v>726</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>677</v>
+        <v>714</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>690</v>
+        <v>727</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>691</v>
+        <v>728</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>677</v>
+        <v>714</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>692</v>
+        <v>729</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>693</v>
+        <v>730</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>677</v>
+        <v>714</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>694</v>
+        <v>731</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>695</v>
+        <v>732</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>696</v>
+        <v>733</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
-        <v>697</v>
+        <v>734</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>698</v>
+        <v>735</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>696</v>
+        <v>733</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
-        <v>699</v>
+        <v>736</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>700</v>
+        <v>737</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>696</v>
+        <v>733</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
-        <v>701</v>
+        <v>738</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>702</v>
+        <v>739</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>696</v>
+        <v>733</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
-        <v>703</v>
+        <v>740</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>704</v>
+        <v>741</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>696</v>
+        <v>733</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
-        <v>705</v>
+        <v>742</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>706</v>
+        <v>743</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>696</v>
+        <v>733</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2" t="s">
-        <v>707</v>
+        <v>744</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>708</v>
+        <v>745</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>696</v>
+        <v>733</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
-        <v>709</v>
+        <v>746</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>710</v>
+        <v>747</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>696</v>
+        <v>733</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
-        <v>711</v>
+        <v>748</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>712</v>
+        <v>749</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>713</v>
+        <v>750</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
-        <v>714</v>
+        <v>751</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>715</v>
+        <v>752</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>713</v>
+        <v>750</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2" t="s">
-        <v>716</v>
+        <v>753</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>717</v>
+        <v>754</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>713</v>
+        <v>750</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2" t="s">
-        <v>718</v>
+        <v>755</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>719</v>
+        <v>756</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>713</v>
+        <v>750</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
-        <v>720</v>
+        <v>757</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>721</v>
+        <v>758</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>713</v>
+        <v>750</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2" t="s">
-        <v>722</v>
+        <v>759</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>723</v>
+        <v>760</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>713</v>
+        <v>750</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2" t="s">
-        <v>724</v>
+        <v>761</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>725</v>
+        <v>762</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>713</v>
+        <v>750</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="2" t="s">
-        <v>726</v>
+        <v>763</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>727</v>
+        <v>764</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>713</v>
+        <v>750</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="2" t="s">
-        <v>728</v>
+        <v>765</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>729</v>
+        <v>766</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>730</v>
+        <v>767</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="2" t="s">
-        <v>731</v>
+        <v>768</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>732</v>
+        <v>769</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>730</v>
+        <v>767</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="2" t="s">
-        <v>733</v>
+        <v>770</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>734</v>
+        <v>771</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>730</v>
+        <v>767</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="2" t="s">
-        <v>735</v>
+        <v>772</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>736</v>
+        <v>773</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>730</v>
+        <v>767</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="2" t="s">
-        <v>737</v>
+        <v>774</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>738</v>
+        <v>775</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>730</v>
+        <v>767</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="2" t="s">
-        <v>739</v>
+        <v>776</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>740</v>
+        <v>777</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>730</v>
+        <v>767</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="2" t="s">
-        <v>741</v>
+        <v>778</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>742</v>
+        <v>779</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>730</v>
+        <v>767</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="2" t="s">
-        <v>743</v>
+        <v>780</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>744</v>
+        <v>781</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>745</v>
+        <v>782</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="2" t="s">
-        <v>746</v>
+        <v>783</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>747</v>
+        <v>784</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>745</v>
+        <v>782</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="2" t="s">
-        <v>748</v>
+        <v>785</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>749</v>
+        <v>786</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>745</v>
+        <v>782</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="2" t="s">
-        <v>750</v>
+        <v>787</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>745</v>
+        <v>782</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="2" t="s">
-        <v>752</v>
+        <v>789</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>753</v>
+        <v>790</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>745</v>
+        <v>782</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="2" t="s">
-        <v>527</v>
+        <v>564</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>754</v>
+        <v>791</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>745</v>
+        <v>782</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="2" t="s">
-        <v>755</v>
+        <v>792</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>756</v>
+        <v>793</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>757</v>
+        <v>794</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="2" t="s">
-        <v>758</v>
+        <v>795</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>759</v>
+        <v>796</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>757</v>
+        <v>794</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="2" t="s">
-        <v>760</v>
+        <v>797</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>761</v>
+        <v>798</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>757</v>
+        <v>794</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="2" t="s">
-        <v>762</v>
+        <v>799</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>763</v>
+        <v>800</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>757</v>
+        <v>794</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="2" t="s">
-        <v>764</v>
+        <v>801</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>765</v>
+        <v>802</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>766</v>
+        <v>803</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="2" t="s">
-        <v>767</v>
+        <v>804</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>768</v>
+        <v>805</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>766</v>
+        <v>803</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="2" t="s">
-        <v>769</v>
+        <v>806</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>770</v>
+        <v>807</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>766</v>
+        <v>803</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="2" t="s">
-        <v>771</v>
+        <v>808</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>766</v>
+        <v>803</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="2" t="s">
-        <v>773</v>
+        <v>810</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>774</v>
+        <v>811</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>766</v>
+        <v>803</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="2" t="s">
-        <v>775</v>
+        <v>812</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>776</v>
+        <v>813</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>766</v>
+        <v>803</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="2" t="s">
-        <v>777</v>
+        <v>814</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>778</v>
+        <v>815</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>766</v>
+        <v>803</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="2" t="s">
-        <v>779</v>
+        <v>816</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>780</v>
+        <v>817</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>766</v>
+        <v>803</v>
       </c>
     </row>
   </sheetData>
